--- a/Projects/Coral/All_OFAVS_to_be_extracted.xlsx
+++ b/Projects/Coral/All_OFAVS_to_be_extracted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thefr\GWNotebook2Repo\LabNotebook2\Projects\Coral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{079D2AD9-33EE-47D0-937B-186F7D5116FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F628762-7FEC-46D4-B5D9-41BB0C07FC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A2FA1217-50A7-4068-99C8-22A486351A14}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="234">
   <si>
     <t>OFAV</t>
   </si>
@@ -684,6 +684,63 @@
   </si>
   <si>
     <t>COL_SAN_Protran1_348</t>
+  </si>
+  <si>
+    <t>Month_year</t>
+  </si>
+  <si>
+    <t>SampleDate</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Experiment</t>
+  </si>
+  <si>
+    <t>Timepoint</t>
+  </si>
+  <si>
+    <t>Person_sampling</t>
+  </si>
+  <si>
+    <t>Tank</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Health_status</t>
+  </si>
+  <si>
+    <t>Sample_type</t>
+  </si>
+  <si>
+    <t>Sample_num</t>
+  </si>
+  <si>
+    <t>Sample_box_num</t>
+  </si>
+  <si>
+    <t>Genet</t>
+  </si>
+  <si>
+    <t>Tubelabel</t>
+  </si>
+  <si>
+    <t>Water_temp</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Sample_physical_location</t>
   </si>
 </sst>
 </file>
@@ -1055,66 +1112,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70FAB1B-F534-4DA3-81C1-119E26A1D085}">
-  <dimension ref="A1:S137"/>
+  <dimension ref="A1:S138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="18" max="18" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>102025</v>
+      <c r="A1" t="s">
+        <v>215</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>216</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>217</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1">
-        <v>1</v>
+        <v>219</v>
+      </c>
+      <c r="F1" t="s">
+        <v>220</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1">
-        <v>33</v>
+        <v>221</v>
+      </c>
+      <c r="H1" t="s">
+        <v>222</v>
       </c>
       <c r="I1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1">
-        <v>33</v>
+        <v>223</v>
+      </c>
+      <c r="J1" t="s">
+        <v>224</v>
       </c>
       <c r="K1" t="s">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="L1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1">
-        <v>33</v>
-      </c>
-      <c r="N1">
-        <v>1</v>
-      </c>
-      <c r="O1">
-        <v>285</v>
+        <v>226</v>
+      </c>
+      <c r="M1" t="s">
+        <v>227</v>
+      </c>
+      <c r="N1" t="s">
+        <v>228</v>
+      </c>
+      <c r="O1" t="s">
+        <v>229</v>
       </c>
       <c r="P1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1">
-        <v>29.6</v>
+        <v>230</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>231</v>
+      </c>
+      <c r="R1" t="s">
+        <v>232</v>
       </c>
       <c r="S1" t="s">
-        <v>9</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -1140,13 +1200,13 @@
         <v>7</v>
       </c>
       <c r="H2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K2" t="s">
         <v>1</v>
@@ -1155,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="M2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -1164,13 +1224,10 @@
         <v>285</v>
       </c>
       <c r="P2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q2">
-        <v>29.4</v>
-      </c>
-      <c r="R2" t="s">
-        <v>11</v>
+        <v>29.6</v>
       </c>
       <c r="S2" t="s">
         <v>9</v>
@@ -1199,22 +1256,22 @@
         <v>7</v>
       </c>
       <c r="H3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
         <v>0</v>
       </c>
       <c r="J3">
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M3">
         <v>34</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>35</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -1223,10 +1280,10 @@
         <v>285</v>
       </c>
       <c r="P3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q3">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="R3" t="s">
         <v>11</v>
@@ -1258,22 +1315,22 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
       </c>
       <c r="J4">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>35</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>36</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -1282,10 +1339,10 @@
         <v>285</v>
       </c>
       <c r="P4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q4">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="R4" t="s">
         <v>11</v>
@@ -1317,22 +1374,22 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
         <v>0</v>
       </c>
       <c r="J5">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>36</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>37</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -1341,10 +1398,10 @@
         <v>285</v>
       </c>
       <c r="P5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q5">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="R5" t="s">
         <v>11</v>
@@ -1376,22 +1433,22 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
         <v>0</v>
       </c>
       <c r="J6">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>37</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>38</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -1400,10 +1457,10 @@
         <v>285</v>
       </c>
       <c r="P6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q6">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="R6" t="s">
         <v>11</v>
@@ -1435,13 +1492,13 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I7" t="s">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K7" t="s">
         <v>1</v>
@@ -1450,7 +1507,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -1459,10 +1516,10 @@
         <v>285</v>
       </c>
       <c r="P7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q7">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="R7" t="s">
         <v>11</v>
@@ -1494,13 +1551,13 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K8" t="s">
         <v>1</v>
@@ -1509,7 +1566,7 @@
         <v>2</v>
       </c>
       <c r="M8">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -1518,7 +1575,7 @@
         <v>285</v>
       </c>
       <c r="P8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q8">
         <v>29.1</v>
@@ -1553,13 +1610,13 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K9" t="s">
         <v>1</v>
@@ -1568,7 +1625,7 @@
         <v>2</v>
       </c>
       <c r="M9">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -1577,10 +1634,10 @@
         <v>285</v>
       </c>
       <c r="P9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q9">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="R9" t="s">
         <v>11</v>
@@ -1612,13 +1669,13 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K10" t="s">
         <v>1</v>
@@ -1627,7 +1684,7 @@
         <v>2</v>
       </c>
       <c r="M10">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N10">
         <v>1</v>
@@ -1636,7 +1693,7 @@
         <v>285</v>
       </c>
       <c r="P10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q10">
         <v>29</v>
@@ -1671,13 +1728,13 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I11" t="s">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K11" t="s">
         <v>1</v>
@@ -1686,7 +1743,7 @@
         <v>2</v>
       </c>
       <c r="M11">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -1695,10 +1752,10 @@
         <v>285</v>
       </c>
       <c r="P11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q11">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="R11" t="s">
         <v>11</v>
@@ -1730,13 +1787,13 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K12" t="s">
         <v>1</v>
@@ -1745,7 +1802,7 @@
         <v>2</v>
       </c>
       <c r="M12">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -1754,7 +1811,7 @@
         <v>285</v>
       </c>
       <c r="P12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q12">
         <v>28.9</v>
@@ -1789,13 +1846,13 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I13" t="s">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K13" t="s">
         <v>1</v>
@@ -1804,7 +1861,7 @@
         <v>2</v>
       </c>
       <c r="M13">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -1813,10 +1870,10 @@
         <v>285</v>
       </c>
       <c r="P13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q13">
-        <v>29.3</v>
+        <v>28.9</v>
       </c>
       <c r="R13" t="s">
         <v>11</v>
@@ -1848,13 +1905,13 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K14" t="s">
         <v>1</v>
@@ -1863,7 +1920,7 @@
         <v>2</v>
       </c>
       <c r="M14">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -1872,13 +1929,13 @@
         <v>285</v>
       </c>
       <c r="P14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q14">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="R14" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="S14" t="s">
         <v>9</v>
@@ -1907,13 +1964,13 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I15" t="s">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K15" t="s">
         <v>1</v>
@@ -1922,7 +1979,7 @@
         <v>2</v>
       </c>
       <c r="M15">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -1931,13 +1988,13 @@
         <v>285</v>
       </c>
       <c r="P15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q15">
-        <v>29</v>
+        <v>29.4</v>
       </c>
       <c r="R15" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="S15" t="s">
         <v>9</v>
@@ -1966,13 +2023,13 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16" t="s">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K16" t="s">
         <v>1</v>
@@ -1981,7 +2038,7 @@
         <v>2</v>
       </c>
       <c r="M16">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -1990,10 +2047,10 @@
         <v>285</v>
       </c>
       <c r="P16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q16">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="R16" t="s">
         <v>11</v>
@@ -2025,13 +2082,13 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I17" t="s">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="K17" t="s">
         <v>1</v>
@@ -2040,22 +2097,22 @@
         <v>2</v>
       </c>
       <c r="M17">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
       <c r="O17">
-        <v>9</v>
+        <v>285</v>
       </c>
       <c r="P17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q17">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="R17" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="S17" t="s">
         <v>9</v>
@@ -2084,13 +2141,13 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I18" t="s">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K18" t="s">
         <v>1</v>
@@ -2099,22 +2156,25 @@
         <v>2</v>
       </c>
       <c r="M18">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O18">
         <v>9</v>
       </c>
       <c r="P18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q18">
-        <v>29.8</v>
+        <v>30</v>
+      </c>
+      <c r="R18" t="s">
+        <v>28</v>
       </c>
       <c r="S18" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -2140,13 +2200,13 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I19" t="s">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s">
         <v>1</v>
@@ -2155,7 +2215,7 @@
         <v>2</v>
       </c>
       <c r="M19">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N19">
         <v>2</v>
@@ -2164,10 +2224,10 @@
         <v>9</v>
       </c>
       <c r="P19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q19">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="S19" t="s">
         <v>30</v>
@@ -2196,13 +2256,13 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I20" t="s">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K20" t="s">
         <v>1</v>
@@ -2211,7 +2271,7 @@
         <v>2</v>
       </c>
       <c r="M20">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N20">
         <v>2</v>
@@ -2220,10 +2280,10 @@
         <v>9</v>
       </c>
       <c r="P20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q20">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="S20" t="s">
         <v>30</v>
@@ -2252,13 +2312,13 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K21" t="s">
         <v>1</v>
@@ -2267,7 +2327,7 @@
         <v>2</v>
       </c>
       <c r="M21">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N21">
         <v>2</v>
@@ -2276,13 +2336,10 @@
         <v>9</v>
       </c>
       <c r="P21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q21">
-        <v>29.9</v>
-      </c>
-      <c r="R21" t="s">
-        <v>34</v>
+        <v>29.8</v>
       </c>
       <c r="S21" t="s">
         <v>30</v>
@@ -2311,13 +2368,13 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I22" t="s">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s">
         <v>1</v>
@@ -2326,7 +2383,7 @@
         <v>2</v>
       </c>
       <c r="M22">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N22">
         <v>2</v>
@@ -2335,10 +2392,13 @@
         <v>9</v>
       </c>
       <c r="P22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q22">
-        <v>29.5</v>
+        <v>29.9</v>
+      </c>
+      <c r="R22" t="s">
+        <v>34</v>
       </c>
       <c r="S22" t="s">
         <v>30</v>
@@ -2367,13 +2427,13 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I23" t="s">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K23" t="s">
         <v>1</v>
@@ -2382,7 +2442,7 @@
         <v>2</v>
       </c>
       <c r="M23">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N23">
         <v>2</v>
@@ -2391,10 +2451,10 @@
         <v>9</v>
       </c>
       <c r="P23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q23">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="S23" t="s">
         <v>30</v>
@@ -2423,13 +2483,13 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I24" t="s">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s">
         <v>1</v>
@@ -2438,7 +2498,7 @@
         <v>2</v>
       </c>
       <c r="M24">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N24">
         <v>2</v>
@@ -2447,10 +2507,10 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q24">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="S24" t="s">
         <v>30</v>
@@ -2479,13 +2539,13 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I25" t="s">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s">
         <v>1</v>
@@ -2494,7 +2554,7 @@
         <v>2</v>
       </c>
       <c r="M25">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N25">
         <v>2</v>
@@ -2503,10 +2563,10 @@
         <v>9</v>
       </c>
       <c r="P25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q25">
-        <v>29.5</v>
+        <v>29.9</v>
       </c>
       <c r="S25" t="s">
         <v>30</v>
@@ -2535,13 +2595,13 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I26" t="s">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s">
         <v>1</v>
@@ -2550,7 +2610,7 @@
         <v>2</v>
       </c>
       <c r="M26">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N26">
         <v>2</v>
@@ -2559,14 +2619,11 @@
         <v>9</v>
       </c>
       <c r="P26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q26">
         <v>29.5</v>
       </c>
-      <c r="R26" t="s">
-        <v>40</v>
-      </c>
       <c r="S26" t="s">
         <v>30</v>
       </c>
@@ -2594,13 +2651,13 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I27" t="s">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s">
         <v>1</v>
@@ -2609,7 +2666,7 @@
         <v>2</v>
       </c>
       <c r="M27">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -2618,10 +2675,13 @@
         <v>9</v>
       </c>
       <c r="P27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q27">
-        <v>29.3</v>
+        <v>29.5</v>
+      </c>
+      <c r="R27" t="s">
+        <v>40</v>
       </c>
       <c r="S27" t="s">
         <v>30</v>
@@ -2650,13 +2710,13 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I28" t="s">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s">
         <v>1</v>
@@ -2665,7 +2725,7 @@
         <v>2</v>
       </c>
       <c r="M28">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N28">
         <v>2</v>
@@ -2674,10 +2734,10 @@
         <v>9</v>
       </c>
       <c r="P28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q28">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="S28" t="s">
         <v>30</v>
@@ -2706,13 +2766,13 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I29" t="s">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s">
         <v>1</v>
@@ -2721,7 +2781,7 @@
         <v>2</v>
       </c>
       <c r="M29">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -2730,7 +2790,7 @@
         <v>9</v>
       </c>
       <c r="P29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q29">
         <v>29.5</v>
@@ -2762,13 +2822,13 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K30" t="s">
         <v>1</v>
@@ -2777,7 +2837,7 @@
         <v>2</v>
       </c>
       <c r="M30">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N30">
         <v>2</v>
@@ -2786,10 +2846,10 @@
         <v>9</v>
       </c>
       <c r="P30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q30">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="S30" t="s">
         <v>30</v>
@@ -2818,13 +2878,13 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I31" t="s">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s">
         <v>1</v>
@@ -2833,7 +2893,7 @@
         <v>2</v>
       </c>
       <c r="M31">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N31">
         <v>2</v>
@@ -2842,10 +2902,10 @@
         <v>9</v>
       </c>
       <c r="P31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q31">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="S31" t="s">
         <v>30</v>
@@ -2874,13 +2934,13 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I32" t="s">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s">
         <v>1</v>
@@ -2889,7 +2949,7 @@
         <v>2</v>
       </c>
       <c r="M32">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -2898,7 +2958,7 @@
         <v>9</v>
       </c>
       <c r="P32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q32">
         <v>29.2</v>
@@ -2930,13 +2990,13 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="K33" t="s">
         <v>1</v>
@@ -2945,19 +3005,19 @@
         <v>2</v>
       </c>
       <c r="M33">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="N33">
         <v>2</v>
       </c>
       <c r="O33">
-        <v>293</v>
+        <v>9</v>
       </c>
       <c r="P33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q33">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="S33" t="s">
         <v>30</v>
@@ -2986,13 +3046,13 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I34" t="s">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K34" t="s">
         <v>1</v>
@@ -3001,7 +3061,7 @@
         <v>2</v>
       </c>
       <c r="M34">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N34">
         <v>2</v>
@@ -3010,10 +3070,10 @@
         <v>293</v>
       </c>
       <c r="P34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q34">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="S34" t="s">
         <v>30</v>
@@ -3042,13 +3102,13 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I35" t="s">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K35" t="s">
         <v>1</v>
@@ -3057,7 +3117,7 @@
         <v>2</v>
       </c>
       <c r="M35">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N35">
         <v>2</v>
@@ -3066,10 +3126,10 @@
         <v>293</v>
       </c>
       <c r="P35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q35">
-        <v>29.8</v>
+        <v>29.3</v>
       </c>
       <c r="S35" t="s">
         <v>30</v>
@@ -3098,13 +3158,13 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I36" t="s">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K36" t="s">
         <v>1</v>
@@ -3113,7 +3173,7 @@
         <v>2</v>
       </c>
       <c r="M36">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N36">
         <v>2</v>
@@ -3122,10 +3182,10 @@
         <v>293</v>
       </c>
       <c r="P36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q36">
-        <v>29.1</v>
+        <v>29.8</v>
       </c>
       <c r="S36" t="s">
         <v>30</v>
@@ -3154,13 +3214,13 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I37" t="s">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K37" t="s">
         <v>1</v>
@@ -3169,7 +3229,7 @@
         <v>2</v>
       </c>
       <c r="M37">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N37">
         <v>2</v>
@@ -3178,10 +3238,10 @@
         <v>293</v>
       </c>
       <c r="P37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q37">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="S37" t="s">
         <v>30</v>
@@ -3210,13 +3270,13 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I38" t="s">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K38" t="s">
         <v>1</v>
@@ -3225,7 +3285,7 @@
         <v>2</v>
       </c>
       <c r="M38">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N38">
         <v>2</v>
@@ -3234,10 +3294,10 @@
         <v>293</v>
       </c>
       <c r="P38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q38">
-        <v>28.9</v>
+        <v>29.4</v>
       </c>
       <c r="S38" t="s">
         <v>30</v>
@@ -3266,13 +3326,13 @@
         <v>7</v>
       </c>
       <c r="H39">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I39" t="s">
         <v>0</v>
       </c>
       <c r="J39">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K39" t="s">
         <v>1</v>
@@ -3281,7 +3341,7 @@
         <v>2</v>
       </c>
       <c r="M39">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N39">
         <v>2</v>
@@ -3290,7 +3350,7 @@
         <v>293</v>
       </c>
       <c r="P39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q39">
         <v>28.9</v>
@@ -3322,13 +3382,13 @@
         <v>7</v>
       </c>
       <c r="H40">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I40" t="s">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K40" t="s">
         <v>1</v>
@@ -3337,7 +3397,7 @@
         <v>2</v>
       </c>
       <c r="M40">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N40">
         <v>2</v>
@@ -3346,10 +3406,10 @@
         <v>293</v>
       </c>
       <c r="P40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q40">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="S40" t="s">
         <v>30</v>
@@ -3378,13 +3438,13 @@
         <v>7</v>
       </c>
       <c r="H41">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I41" t="s">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K41" t="s">
         <v>1</v>
@@ -3393,7 +3453,7 @@
         <v>2</v>
       </c>
       <c r="M41">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N41">
         <v>2</v>
@@ -3402,10 +3462,10 @@
         <v>293</v>
       </c>
       <c r="P41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q41">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="S41" t="s">
         <v>30</v>
@@ -3434,13 +3494,13 @@
         <v>7</v>
       </c>
       <c r="H42">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I42" t="s">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K42" t="s">
         <v>1</v>
@@ -3449,7 +3509,7 @@
         <v>2</v>
       </c>
       <c r="M42">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N42">
         <v>2</v>
@@ -3458,10 +3518,10 @@
         <v>293</v>
       </c>
       <c r="P42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q42">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="S42" t="s">
         <v>30</v>
@@ -3490,13 +3550,13 @@
         <v>7</v>
       </c>
       <c r="H43">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I43" t="s">
         <v>0</v>
       </c>
       <c r="J43">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K43" t="s">
         <v>1</v>
@@ -3505,7 +3565,7 @@
         <v>2</v>
       </c>
       <c r="M43">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N43">
         <v>2</v>
@@ -3514,10 +3574,10 @@
         <v>293</v>
       </c>
       <c r="P43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q43">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="S43" t="s">
         <v>30</v>
@@ -3546,13 +3606,13 @@
         <v>7</v>
       </c>
       <c r="H44">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I44" t="s">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K44" t="s">
         <v>1</v>
@@ -3561,7 +3621,7 @@
         <v>2</v>
       </c>
       <c r="M44">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N44">
         <v>2</v>
@@ -3570,10 +3630,10 @@
         <v>293</v>
       </c>
       <c r="P44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q44">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="S44" t="s">
         <v>30</v>
@@ -3602,13 +3662,13 @@
         <v>7</v>
       </c>
       <c r="H45">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I45" t="s">
         <v>0</v>
       </c>
       <c r="J45">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K45" t="s">
         <v>1</v>
@@ -3617,7 +3677,7 @@
         <v>2</v>
       </c>
       <c r="M45">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N45">
         <v>2</v>
@@ -3626,10 +3686,10 @@
         <v>293</v>
       </c>
       <c r="P45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q45">
-        <v>28.5</v>
+        <v>28.8</v>
       </c>
       <c r="S45" t="s">
         <v>30</v>
@@ -3658,13 +3718,13 @@
         <v>7</v>
       </c>
       <c r="H46">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I46" t="s">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K46" t="s">
         <v>1</v>
@@ -3673,7 +3733,7 @@
         <v>2</v>
       </c>
       <c r="M46">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N46">
         <v>2</v>
@@ -3682,7 +3742,7 @@
         <v>293</v>
       </c>
       <c r="P46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q46">
         <v>28.5</v>
@@ -3714,13 +3774,13 @@
         <v>7</v>
       </c>
       <c r="H47">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I47" t="s">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K47" t="s">
         <v>1</v>
@@ -3729,7 +3789,7 @@
         <v>2</v>
       </c>
       <c r="M47">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N47">
         <v>2</v>
@@ -3738,10 +3798,10 @@
         <v>293</v>
       </c>
       <c r="P47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q47">
-        <v>28.1</v>
+        <v>28.5</v>
       </c>
       <c r="S47" t="s">
         <v>30</v>
@@ -3770,13 +3830,13 @@
         <v>7</v>
       </c>
       <c r="H48">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I48" t="s">
         <v>0</v>
       </c>
       <c r="J48">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K48" t="s">
         <v>1</v>
@@ -3785,7 +3845,7 @@
         <v>2</v>
       </c>
       <c r="M48">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N48">
         <v>2</v>
@@ -3794,10 +3854,10 @@
         <v>293</v>
       </c>
       <c r="P48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q48">
-        <v>28.9</v>
+        <v>28.1</v>
       </c>
       <c r="S48" t="s">
         <v>30</v>
@@ -3808,7 +3868,7 @@
         <v>102025</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C49" t="s">
         <v>4</v>
@@ -3820,19 +3880,19 @@
         <v>6</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="H49">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I49" t="s">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="K49" t="s">
         <v>1</v>
@@ -3841,16 +3901,19 @@
         <v>2</v>
       </c>
       <c r="M49">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="N49">
         <v>2</v>
       </c>
+      <c r="O49">
+        <v>293</v>
+      </c>
       <c r="P49" t="s">
-        <v>65</v>
-      </c>
-      <c r="R49" t="s">
-        <v>66</v>
+        <v>62</v>
+      </c>
+      <c r="Q49">
+        <v>28.9</v>
       </c>
       <c r="S49" t="s">
         <v>30</v>
@@ -3885,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s">
         <v>1</v>
@@ -3894,16 +3957,16 @@
         <v>2</v>
       </c>
       <c r="M50">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N50">
         <v>2</v>
       </c>
       <c r="P50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R50" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="S50" t="s">
         <v>30</v>
@@ -3938,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="K51" t="s">
         <v>1</v>
@@ -3947,16 +4010,16 @@
         <v>2</v>
       </c>
       <c r="M51">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N51">
         <v>2</v>
       </c>
       <c r="P51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="R51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S51" t="s">
         <v>30</v>
@@ -3985,13 +4048,13 @@
         <v>64</v>
       </c>
       <c r="H52">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I52" t="s">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="K52" t="s">
         <v>1</v>
@@ -4000,13 +4063,16 @@
         <v>2</v>
       </c>
       <c r="M52">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N52">
         <v>2</v>
       </c>
       <c r="P52" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="R52" t="s">
+        <v>70</v>
       </c>
       <c r="S52" t="s">
         <v>30</v>
@@ -4041,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="K53" t="s">
         <v>1</v>
@@ -4050,16 +4116,13 @@
         <v>2</v>
       </c>
       <c r="M53">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N53">
         <v>2</v>
       </c>
       <c r="P53" t="s">
-        <v>72</v>
-      </c>
-      <c r="R53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S53" t="s">
         <v>30</v>
@@ -4094,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="K54" t="s">
         <v>1</v>
@@ -4103,13 +4166,16 @@
         <v>2</v>
       </c>
       <c r="M54">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N54">
         <v>2</v>
       </c>
       <c r="P54" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="R54" t="s">
+        <v>73</v>
       </c>
       <c r="S54" t="s">
         <v>30</v>
@@ -4138,13 +4204,13 @@
         <v>64</v>
       </c>
       <c r="H55">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I55" t="s">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s">
         <v>1</v>
@@ -4153,16 +4219,13 @@
         <v>2</v>
       </c>
       <c r="M55">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N55">
         <v>2</v>
       </c>
       <c r="P55" t="s">
-        <v>75</v>
-      </c>
-      <c r="R55" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="S55" t="s">
         <v>30</v>
@@ -4197,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="K56" t="s">
         <v>1</v>
@@ -4206,13 +4269,16 @@
         <v>2</v>
       </c>
       <c r="M56">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N56">
         <v>2</v>
       </c>
       <c r="P56" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="R56" t="s">
+        <v>76</v>
       </c>
       <c r="S56" t="s">
         <v>30</v>
@@ -4247,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="K57" t="s">
         <v>1</v>
@@ -4256,16 +4322,13 @@
         <v>2</v>
       </c>
       <c r="M57">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N57">
         <v>2</v>
       </c>
       <c r="P57" t="s">
-        <v>78</v>
-      </c>
-      <c r="R57" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="S57" t="s">
         <v>30</v>
@@ -4294,13 +4357,13 @@
         <v>64</v>
       </c>
       <c r="H58">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I58" t="s">
         <v>0</v>
       </c>
       <c r="J58">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="K58" t="s">
         <v>1</v>
@@ -4309,16 +4372,16 @@
         <v>2</v>
       </c>
       <c r="M58">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N58">
         <v>2</v>
       </c>
       <c r="P58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R58" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="S58" t="s">
         <v>30</v>
@@ -4353,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="K59" t="s">
         <v>1</v>
@@ -4362,13 +4425,16 @@
         <v>2</v>
       </c>
       <c r="M59">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N59">
         <v>2</v>
       </c>
       <c r="P59" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="R59" t="s">
+        <v>80</v>
       </c>
       <c r="S59" t="s">
         <v>30</v>
@@ -4403,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="K60" t="s">
         <v>1</v>
@@ -4412,16 +4478,13 @@
         <v>2</v>
       </c>
       <c r="M60">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N60">
         <v>2</v>
       </c>
       <c r="P60" t="s">
-        <v>82</v>
-      </c>
-      <c r="R60" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="S60" t="s">
         <v>30</v>
@@ -4450,13 +4513,13 @@
         <v>64</v>
       </c>
       <c r="H61">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I61" t="s">
         <v>0</v>
       </c>
       <c r="J61">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="K61" t="s">
         <v>1</v>
@@ -4465,19 +4528,19 @@
         <v>2</v>
       </c>
       <c r="M61">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R61" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="S61" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
@@ -4509,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="K62" t="s">
         <v>1</v>
@@ -4518,16 +4581,16 @@
         <v>2</v>
       </c>
       <c r="M62">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N62">
         <v>3</v>
       </c>
       <c r="P62" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="R62" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="S62" t="s">
         <v>86</v>
@@ -4562,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>36</v>
+        <v>133</v>
       </c>
       <c r="K63" t="s">
         <v>1</v>
@@ -4571,16 +4634,16 @@
         <v>2</v>
       </c>
       <c r="M63">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N63">
         <v>3</v>
       </c>
       <c r="P63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R63" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="S63" t="s">
         <v>86</v>
@@ -4609,31 +4672,31 @@
         <v>64</v>
       </c>
       <c r="H64">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I64" t="s">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K64" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="L64" t="s">
         <v>2</v>
       </c>
       <c r="M64">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N64">
         <v>3</v>
       </c>
       <c r="P64" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="R64" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="S64" t="s">
         <v>86</v>
@@ -4668,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="K65" t="s">
         <v>90</v>
@@ -4677,16 +4740,16 @@
         <v>2</v>
       </c>
       <c r="M65">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N65">
         <v>3</v>
       </c>
       <c r="P65" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R65" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S65" t="s">
         <v>86</v>
@@ -4721,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="K66" t="s">
         <v>90</v>
@@ -4730,16 +4793,16 @@
         <v>2</v>
       </c>
       <c r="M66">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N66">
         <v>3</v>
       </c>
       <c r="P66" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="R66" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S66" t="s">
         <v>86</v>
@@ -4768,28 +4831,31 @@
         <v>64</v>
       </c>
       <c r="H67">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I67" t="s">
         <v>0</v>
       </c>
       <c r="J67">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K67" t="s">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="L67" t="s">
         <v>2</v>
       </c>
       <c r="M67">
-        <v>211</v>
+        <v>210</v>
+      </c>
+      <c r="N67">
+        <v>3</v>
       </c>
       <c r="P67" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R67" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S67" t="s">
         <v>86</v>
@@ -4824,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="K68" t="s">
         <v>1</v>
@@ -4833,13 +4899,13 @@
         <v>2</v>
       </c>
       <c r="M68">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P68" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="R68" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S68" t="s">
         <v>86</v>
@@ -4874,22 +4940,22 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="K69" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L69" t="s">
         <v>2</v>
       </c>
       <c r="M69">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P69" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="R69" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="S69" t="s">
         <v>86</v>
@@ -4918,13 +4984,13 @@
         <v>64</v>
       </c>
       <c r="H70">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I70" t="s">
         <v>0</v>
       </c>
       <c r="J70">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K70" t="s">
         <v>11</v>
@@ -4933,10 +4999,10 @@
         <v>2</v>
       </c>
       <c r="M70">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P70" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R70" t="s">
         <v>11</v>
@@ -4974,22 +5040,22 @@
         <v>0</v>
       </c>
       <c r="J71">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="K71" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="L71" t="s">
         <v>2</v>
       </c>
       <c r="M71">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P71" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R71" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="S71" t="s">
         <v>86</v>
@@ -5024,22 +5090,22 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="K72" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="L72" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M72">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P72" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R72" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="S72" t="s">
         <v>86</v>
@@ -5076,14 +5142,17 @@
       <c r="J73">
         <v>88</v>
       </c>
+      <c r="K73" t="s">
+        <v>90</v>
+      </c>
       <c r="L73" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M73">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P73" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R73" t="s">
         <v>107</v>
@@ -5115,28 +5184,25 @@
         <v>64</v>
       </c>
       <c r="H74">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I74" t="s">
         <v>0</v>
       </c>
       <c r="J74">
-        <v>41</v>
-      </c>
-      <c r="K74" t="s">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="L74" t="s">
         <v>2</v>
       </c>
       <c r="M74">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="P74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R74" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="S74" t="s">
         <v>86</v>
@@ -5171,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="J75">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="K75" t="s">
         <v>1</v>
@@ -5180,13 +5246,13 @@
         <v>2</v>
       </c>
       <c r="M75">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P75" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R75" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="S75" t="s">
         <v>86</v>
@@ -5221,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="J76">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="K76" t="s">
         <v>1</v>
@@ -5230,10 +5296,13 @@
         <v>2</v>
       </c>
       <c r="M76">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P76" t="s">
-        <v>112</v>
+        <v>111</v>
+      </c>
+      <c r="R76" t="s">
+        <v>11</v>
       </c>
       <c r="S76" t="s">
         <v>86</v>
@@ -5262,13 +5331,13 @@
         <v>64</v>
       </c>
       <c r="H77">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I77" t="s">
         <v>0</v>
       </c>
       <c r="J77">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s">
         <v>1</v>
@@ -5277,10 +5346,10 @@
         <v>2</v>
       </c>
       <c r="M77">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="S77" t="s">
         <v>86</v>
@@ -5315,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="J78">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s">
         <v>1</v>
@@ -5324,10 +5393,10 @@
         <v>2</v>
       </c>
       <c r="M78">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S78" t="s">
         <v>86</v>
@@ -5362,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="J79">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="K79" t="s">
         <v>1</v>
@@ -5371,13 +5440,10 @@
         <v>2</v>
       </c>
       <c r="M79">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P79" t="s">
-        <v>115</v>
-      </c>
-      <c r="R79" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="S79" t="s">
         <v>86</v>
@@ -5406,13 +5472,13 @@
         <v>64</v>
       </c>
       <c r="H80">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
       </c>
       <c r="J80">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="K80" t="s">
         <v>1</v>
@@ -5421,10 +5487,13 @@
         <v>2</v>
       </c>
       <c r="M80">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P80" t="s">
-        <v>117</v>
+        <v>115</v>
+      </c>
+      <c r="R80" t="s">
+        <v>116</v>
       </c>
       <c r="S80" t="s">
         <v>86</v>
@@ -5459,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="J81">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="K81" t="s">
         <v>1</v>
@@ -5468,10 +5537,10 @@
         <v>2</v>
       </c>
       <c r="M81">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P81" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S81" t="s">
         <v>86</v>
@@ -5506,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="J82">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="K82" t="s">
         <v>1</v>
@@ -5515,13 +5584,10 @@
         <v>2</v>
       </c>
       <c r="M82">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P82" t="s">
-        <v>119</v>
-      </c>
-      <c r="R82" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="S82" t="s">
         <v>86</v>
@@ -5550,13 +5616,13 @@
         <v>64</v>
       </c>
       <c r="H83">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I83" t="s">
         <v>0</v>
       </c>
       <c r="J83">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="K83" t="s">
         <v>1</v>
@@ -5565,10 +5631,13 @@
         <v>2</v>
       </c>
       <c r="M83">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P83" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="R83" t="s">
+        <v>120</v>
       </c>
       <c r="S83" t="s">
         <v>86</v>
@@ -5603,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="J84">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="K84" t="s">
         <v>1</v>
@@ -5612,13 +5681,10 @@
         <v>2</v>
       </c>
       <c r="M84">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P84" t="s">
-        <v>122</v>
-      </c>
-      <c r="R84" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="S84" t="s">
         <v>86</v>
@@ -5653,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="K85" t="s">
         <v>1</v>
@@ -5662,10 +5728,13 @@
         <v>2</v>
       </c>
       <c r="M85">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P85" t="s">
-        <v>123</v>
+        <v>122</v>
+      </c>
+      <c r="R85" t="s">
+        <v>11</v>
       </c>
       <c r="S85" t="s">
         <v>86</v>
@@ -5694,13 +5763,13 @@
         <v>64</v>
       </c>
       <c r="H86">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I86" t="s">
         <v>0</v>
       </c>
       <c r="J86">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K86" t="s">
         <v>1</v>
@@ -5709,10 +5778,10 @@
         <v>2</v>
       </c>
       <c r="M86">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="P86" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S86" t="s">
         <v>86</v>
@@ -5747,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="J87">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="K87" t="s">
         <v>1</v>
@@ -5756,13 +5825,10 @@
         <v>2</v>
       </c>
       <c r="M87">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P87" t="s">
-        <v>125</v>
-      </c>
-      <c r="R87" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="S87" t="s">
         <v>86</v>
@@ -5797,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="J88">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="K88" t="s">
         <v>1</v>
@@ -5806,13 +5872,13 @@
         <v>2</v>
       </c>
       <c r="M88">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P88" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R88" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S88" t="s">
         <v>86</v>
@@ -5841,13 +5907,13 @@
         <v>64</v>
       </c>
       <c r="H89">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I89" t="s">
         <v>0</v>
       </c>
       <c r="J89">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="K89" t="s">
         <v>1</v>
@@ -5856,13 +5922,13 @@
         <v>2</v>
       </c>
       <c r="M89">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P89" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="R89" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S89" t="s">
         <v>86</v>
@@ -5897,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="K90" t="s">
         <v>1</v>
@@ -5906,13 +5972,16 @@
         <v>2</v>
       </c>
       <c r="M90">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P90" t="s">
-        <v>131</v>
+        <v>129</v>
+      </c>
+      <c r="R90" t="s">
+        <v>130</v>
       </c>
       <c r="S90" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
@@ -5944,7 +6013,7 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="K91" t="s">
         <v>1</v>
@@ -5953,10 +6022,10 @@
         <v>2</v>
       </c>
       <c r="M91">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P91" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="S91" t="s">
         <v>132</v>
@@ -5985,13 +6054,13 @@
         <v>64</v>
       </c>
       <c r="H92">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
       </c>
       <c r="J92">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="K92" t="s">
         <v>1</v>
@@ -6000,10 +6069,10 @@
         <v>2</v>
       </c>
       <c r="M92">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S92" t="s">
         <v>132</v>
@@ -6038,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="J93">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="K93" t="s">
         <v>1</v>
@@ -6047,13 +6116,10 @@
         <v>2</v>
       </c>
       <c r="M93">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P93" t="s">
-        <v>135</v>
-      </c>
-      <c r="R93" t="s">
-        <v>11</v>
+        <v>134</v>
       </c>
       <c r="S93" t="s">
         <v>132</v>
@@ -6088,7 +6154,7 @@
         <v>0</v>
       </c>
       <c r="J94">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="K94" t="s">
         <v>1</v>
@@ -6097,10 +6163,13 @@
         <v>2</v>
       </c>
       <c r="M94">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P94" t="s">
-        <v>136</v>
+        <v>135</v>
+      </c>
+      <c r="R94" t="s">
+        <v>11</v>
       </c>
       <c r="S94" t="s">
         <v>132</v>
@@ -6129,13 +6198,13 @@
         <v>64</v>
       </c>
       <c r="H95">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
       </c>
       <c r="J95">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="K95" t="s">
         <v>1</v>
@@ -6144,13 +6213,10 @@
         <v>2</v>
       </c>
       <c r="M95">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P95" t="s">
-        <v>137</v>
-      </c>
-      <c r="R95" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="S95" t="s">
         <v>132</v>
@@ -6185,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="J96">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="K96" t="s">
         <v>1</v>
@@ -6194,13 +6260,13 @@
         <v>2</v>
       </c>
       <c r="M96">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P96" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R96" t="s">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="S96" t="s">
         <v>132</v>
@@ -6235,7 +6301,7 @@
         <v>0</v>
       </c>
       <c r="J97">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="K97" t="s">
         <v>1</v>
@@ -6244,10 +6310,13 @@
         <v>2</v>
       </c>
       <c r="M97">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P97" t="s">
-        <v>140</v>
+        <v>138</v>
+      </c>
+      <c r="R97" t="s">
+        <v>139</v>
       </c>
       <c r="S97" t="s">
         <v>132</v>
@@ -6276,13 +6345,13 @@
         <v>64</v>
       </c>
       <c r="H98">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="I98" t="s">
         <v>0</v>
       </c>
-      <c r="J98" t="s">
-        <v>141</v>
+      <c r="J98">
+        <v>48</v>
       </c>
       <c r="K98" t="s">
         <v>1</v>
@@ -6291,13 +6360,10 @@
         <v>2</v>
       </c>
       <c r="M98">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P98" t="s">
-        <v>142</v>
-      </c>
-      <c r="R98" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="S98" t="s">
         <v>132</v>
@@ -6326,13 +6392,13 @@
         <v>64</v>
       </c>
       <c r="H99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" t="s">
         <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K99" t="s">
         <v>1</v>
@@ -6341,10 +6407,13 @@
         <v>2</v>
       </c>
       <c r="M99">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P99" t="s">
-        <v>145</v>
+        <v>142</v>
+      </c>
+      <c r="R99" t="s">
+        <v>143</v>
       </c>
       <c r="S99" t="s">
         <v>132</v>
@@ -6373,13 +6442,13 @@
         <v>64</v>
       </c>
       <c r="H100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I100" t="s">
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K100" t="s">
         <v>1</v>
@@ -6388,10 +6457,10 @@
         <v>2</v>
       </c>
       <c r="M100">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P100" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="S100" t="s">
         <v>132</v>
@@ -6420,13 +6489,13 @@
         <v>64</v>
       </c>
       <c r="H101">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I101" t="s">
         <v>0</v>
       </c>
       <c r="J101" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K101" t="s">
         <v>1</v>
@@ -6435,10 +6504,10 @@
         <v>2</v>
       </c>
       <c r="M101">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P101" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="S101" t="s">
         <v>132</v>
@@ -6467,13 +6536,13 @@
         <v>64</v>
       </c>
       <c r="H102">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I102" t="s">
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K102" t="s">
         <v>1</v>
@@ -6482,10 +6551,10 @@
         <v>2</v>
       </c>
       <c r="M102">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P102" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="S102" t="s">
         <v>132</v>
@@ -6514,13 +6583,13 @@
         <v>64</v>
       </c>
       <c r="H103">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I103" t="s">
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K103" t="s">
         <v>1</v>
@@ -6529,10 +6598,10 @@
         <v>2</v>
       </c>
       <c r="M103">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P103" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="S103" t="s">
         <v>132</v>
@@ -6561,13 +6630,13 @@
         <v>64</v>
       </c>
       <c r="H104">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I104" t="s">
         <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K104" t="s">
         <v>1</v>
@@ -6576,10 +6645,10 @@
         <v>2</v>
       </c>
       <c r="M104">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P104" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="S104" t="s">
         <v>132</v>
@@ -6608,13 +6677,13 @@
         <v>64</v>
       </c>
       <c r="H105">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I105" t="s">
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K105" t="s">
         <v>1</v>
@@ -6623,10 +6692,10 @@
         <v>2</v>
       </c>
       <c r="M105">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P105" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="S105" t="s">
         <v>132</v>
@@ -6655,13 +6724,13 @@
         <v>64</v>
       </c>
       <c r="H106">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I106" t="s">
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K106" t="s">
         <v>1</v>
@@ -6670,10 +6739,10 @@
         <v>2</v>
       </c>
       <c r="M106">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P106" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S106" t="s">
         <v>132</v>
@@ -6702,13 +6771,13 @@
         <v>64</v>
       </c>
       <c r="H107">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I107" t="s">
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K107" t="s">
         <v>1</v>
@@ -6717,10 +6786,10 @@
         <v>2</v>
       </c>
       <c r="M107">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P107" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="S107" t="s">
         <v>132</v>
@@ -6749,13 +6818,13 @@
         <v>64</v>
       </c>
       <c r="H108">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I108" t="s">
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K108" t="s">
         <v>1</v>
@@ -6764,13 +6833,10 @@
         <v>2</v>
       </c>
       <c r="M108">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P108" t="s">
-        <v>163</v>
-      </c>
-      <c r="R108" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="S108" t="s">
         <v>132</v>
@@ -6799,13 +6865,13 @@
         <v>64</v>
       </c>
       <c r="H109">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I109" t="s">
         <v>0</v>
       </c>
       <c r="J109" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K109" t="s">
         <v>1</v>
@@ -6814,10 +6880,13 @@
         <v>2</v>
       </c>
       <c r="M109">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P109" t="s">
-        <v>166</v>
+        <v>163</v>
+      </c>
+      <c r="R109" t="s">
+        <v>164</v>
       </c>
       <c r="S109" t="s">
         <v>132</v>
@@ -6846,13 +6915,13 @@
         <v>64</v>
       </c>
       <c r="H110">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I110" t="s">
         <v>0</v>
       </c>
       <c r="J110" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K110" t="s">
         <v>1</v>
@@ -6861,10 +6930,10 @@
         <v>2</v>
       </c>
       <c r="M110">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P110" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="S110" t="s">
         <v>132</v>
@@ -6893,25 +6962,25 @@
         <v>64</v>
       </c>
       <c r="H111">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I111" t="s">
         <v>0</v>
       </c>
       <c r="J111" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K111" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L111" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M111">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="P111" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="S111" t="s">
         <v>132</v>
@@ -6952,16 +7021,13 @@
         <v>170</v>
       </c>
       <c r="L112" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M112">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P112" t="s">
-        <v>172</v>
-      </c>
-      <c r="R112" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S112" t="s">
         <v>132</v>
@@ -6990,28 +7056,28 @@
         <v>64</v>
       </c>
       <c r="H113">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I113" t="s">
         <v>0</v>
       </c>
       <c r="J113" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="K113" t="s">
         <v>170</v>
       </c>
       <c r="L113" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M113">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P113" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="R113" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="S113" t="s">
         <v>132</v>
@@ -7052,13 +7118,16 @@
         <v>170</v>
       </c>
       <c r="L114" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M114">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P114" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="R114" t="s">
+        <v>176</v>
       </c>
       <c r="S114" t="s">
         <v>132</v>
@@ -7087,28 +7156,25 @@
         <v>64</v>
       </c>
       <c r="H115">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I115" t="s">
         <v>0</v>
       </c>
       <c r="J115" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K115" t="s">
         <v>170</v>
       </c>
       <c r="L115" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M115">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P115" t="s">
-        <v>179</v>
-      </c>
-      <c r="R115" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="S115" t="s">
         <v>132</v>
@@ -7149,13 +7215,16 @@
         <v>170</v>
       </c>
       <c r="L116" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M116">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="P116" t="s">
-        <v>181</v>
+        <v>179</v>
+      </c>
+      <c r="R116" t="s">
+        <v>180</v>
       </c>
       <c r="S116" t="s">
         <v>132</v>
@@ -7184,25 +7253,25 @@
         <v>64</v>
       </c>
       <c r="H117">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I117" t="s">
         <v>0</v>
       </c>
       <c r="J117" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K117" t="s">
         <v>170</v>
       </c>
       <c r="L117" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M117">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="P117" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S117" t="s">
         <v>132</v>
@@ -7243,13 +7312,13 @@
         <v>170</v>
       </c>
       <c r="L118" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M118">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P118" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S118" t="s">
         <v>132</v>
@@ -7278,25 +7347,25 @@
         <v>64</v>
       </c>
       <c r="H119">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I119" t="s">
         <v>0</v>
       </c>
       <c r="J119" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K119" t="s">
         <v>170</v>
       </c>
       <c r="L119" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M119">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P119" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="S119" t="s">
         <v>132</v>
@@ -7337,13 +7406,13 @@
         <v>170</v>
       </c>
       <c r="L120" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M120">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P120" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S120" t="s">
         <v>132</v>
@@ -7372,25 +7441,25 @@
         <v>64</v>
       </c>
       <c r="H121">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I121" t="s">
         <v>0</v>
       </c>
       <c r="J121" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K121" t="s">
         <v>170</v>
       </c>
       <c r="L121" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M121">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P121" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="S121" t="s">
         <v>132</v>
@@ -7431,13 +7500,13 @@
         <v>170</v>
       </c>
       <c r="L122" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M122">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P122" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S122" t="s">
         <v>132</v>
@@ -7466,25 +7535,25 @@
         <v>64</v>
       </c>
       <c r="H123">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I123" t="s">
         <v>0</v>
       </c>
       <c r="J123" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="K123" t="s">
         <v>170</v>
       </c>
       <c r="L123" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M123">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P123" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="S123" t="s">
         <v>132</v>
@@ -7525,13 +7594,13 @@
         <v>170</v>
       </c>
       <c r="L124" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M124">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P124" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="S124" t="s">
         <v>132</v>
@@ -7560,25 +7629,25 @@
         <v>64</v>
       </c>
       <c r="H125">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I125" t="s">
         <v>0</v>
       </c>
       <c r="J125" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K125" t="s">
         <v>170</v>
       </c>
       <c r="L125" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M125">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="P125" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="S125" t="s">
         <v>132</v>
@@ -7619,13 +7688,13 @@
         <v>170</v>
       </c>
       <c r="L126" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M126">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P126" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="S126" t="s">
         <v>132</v>
@@ -7654,28 +7723,25 @@
         <v>64</v>
       </c>
       <c r="H127">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I127" t="s">
         <v>0</v>
       </c>
       <c r="J127" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K127" t="s">
         <v>170</v>
       </c>
       <c r="L127" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M127">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P127" t="s">
-        <v>198</v>
-      </c>
-      <c r="R127" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="S127" t="s">
         <v>132</v>
@@ -7704,13 +7770,13 @@
         <v>64</v>
       </c>
       <c r="H128">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I128" t="s">
         <v>0</v>
       </c>
       <c r="J128" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K128" t="s">
         <v>170</v>
@@ -7719,10 +7785,13 @@
         <v>105</v>
       </c>
       <c r="M128">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P128" t="s">
-        <v>201</v>
+        <v>198</v>
+      </c>
+      <c r="R128" t="s">
+        <v>199</v>
       </c>
       <c r="S128" t="s">
         <v>132</v>
@@ -7763,13 +7832,13 @@
         <v>170</v>
       </c>
       <c r="L129" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M129">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P129" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S129" t="s">
         <v>132</v>
@@ -7798,25 +7867,25 @@
         <v>64</v>
       </c>
       <c r="H130">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I130" t="s">
         <v>0</v>
       </c>
       <c r="J130" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K130" t="s">
         <v>170</v>
       </c>
       <c r="L130" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M130">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="P130" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="S130" t="s">
         <v>132</v>
@@ -7857,13 +7926,13 @@
         <v>170</v>
       </c>
       <c r="L131" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M131">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P131" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S131" t="s">
         <v>132</v>
@@ -7892,25 +7961,25 @@
         <v>64</v>
       </c>
       <c r="H132">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I132" t="s">
         <v>0</v>
       </c>
       <c r="J132" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K132" t="s">
         <v>170</v>
       </c>
       <c r="L132" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M132">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P132" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="S132" t="s">
         <v>132</v>
@@ -7951,13 +8020,13 @@
         <v>170</v>
       </c>
       <c r="L133" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M133">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P133" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S133" t="s">
         <v>132</v>
@@ -7986,25 +8055,25 @@
         <v>64</v>
       </c>
       <c r="H134">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I134" t="s">
         <v>0</v>
       </c>
       <c r="J134" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K134" t="s">
         <v>170</v>
       </c>
       <c r="L134" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M134">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P134" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="S134" t="s">
         <v>132</v>
@@ -8045,13 +8114,13 @@
         <v>170</v>
       </c>
       <c r="L135" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M135">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P135" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S135" t="s">
         <v>132</v>
@@ -8080,25 +8149,25 @@
         <v>64</v>
       </c>
       <c r="H136">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I136" t="s">
         <v>0</v>
       </c>
       <c r="J136" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K136" t="s">
         <v>170</v>
       </c>
       <c r="L136" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M136">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P136" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="S136" t="s">
         <v>132</v>
@@ -8139,15 +8208,62 @@
         <v>170</v>
       </c>
       <c r="L137" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M137">
+        <v>347</v>
+      </c>
+      <c r="P137" t="s">
+        <v>213</v>
+      </c>
+      <c r="S137" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>102025</v>
+      </c>
+      <c r="B138" t="s">
+        <v>63</v>
+      </c>
+      <c r="C138" t="s">
+        <v>4</v>
+      </c>
+      <c r="D138" t="s">
+        <v>5</v>
+      </c>
+      <c r="E138" t="s">
+        <v>6</v>
+      </c>
+      <c r="F138">
+        <v>2</v>
+      </c>
+      <c r="G138" t="s">
+        <v>64</v>
+      </c>
+      <c r="H138">
+        <v>32</v>
+      </c>
+      <c r="I138" t="s">
+        <v>0</v>
+      </c>
+      <c r="J138" t="s">
+        <v>212</v>
+      </c>
+      <c r="K138" t="s">
+        <v>170</v>
+      </c>
+      <c r="L138" t="s">
+        <v>2</v>
+      </c>
+      <c r="M138">
         <v>348</v>
       </c>
-      <c r="P137" t="s">
+      <c r="P138" t="s">
         <v>214</v>
       </c>
-      <c r="S137" t="s">
+      <c r="S138" t="s">
         <v>132</v>
       </c>
     </row>

--- a/Projects/Coral/All_OFAVS_to_be_extracted.xlsx
+++ b/Projects/Coral/All_OFAVS_to_be_extracted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thefr\GWNotebook2Repo\LabNotebook2\Projects\Coral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F628762-7FEC-46D4-B5D9-41BB0C07FC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A415EB-1B8E-4D0D-A38C-BD3D1F7269AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A2FA1217-50A7-4068-99C8-22A486351A14}"/>
   </bookViews>
@@ -1115,6 +1115,7 @@
   <dimension ref="A1:S138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="18" max="18" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1256,14 +1257,14 @@
         <v>7</v>
       </c>
       <c r="H3">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>34</v>
       </c>
-      <c r="I3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>38</v>
-      </c>
       <c r="K3" t="s">
         <v>1</v>
       </c>
@@ -1271,7 +1272,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -1280,10 +1281,10 @@
         <v>285</v>
       </c>
       <c r="P3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q3">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="R3" t="s">
         <v>11</v>
@@ -1315,14 +1316,14 @@
         <v>7</v>
       </c>
       <c r="H4">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>35</v>
       </c>
-      <c r="I4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>34</v>
-      </c>
       <c r="K4" t="s">
         <v>1</v>
       </c>
@@ -1330,7 +1331,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -1339,10 +1340,10 @@
         <v>285</v>
       </c>
       <c r="P4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q4">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="R4" t="s">
         <v>11</v>
@@ -1374,14 +1375,14 @@
         <v>7</v>
       </c>
       <c r="H5">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>36</v>
       </c>
-      <c r="I5" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>35</v>
-      </c>
       <c r="K5" t="s">
         <v>1</v>
       </c>
@@ -1389,7 +1390,7 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -1398,10 +1399,10 @@
         <v>285</v>
       </c>
       <c r="P5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q5">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="R5" t="s">
         <v>11</v>
@@ -1433,14 +1434,14 @@
         <v>7</v>
       </c>
       <c r="H6">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>37</v>
       </c>
-      <c r="I6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>36</v>
-      </c>
       <c r="K6" t="s">
         <v>1</v>
       </c>
@@ -1448,7 +1449,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -1457,10 +1458,10 @@
         <v>285</v>
       </c>
       <c r="P6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q6">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="R6" t="s">
         <v>11</v>
@@ -1492,14 +1493,14 @@
         <v>7</v>
       </c>
       <c r="H7">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>38</v>
       </c>
-      <c r="I7" t="s">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>37</v>
-      </c>
       <c r="K7" t="s">
         <v>1</v>
       </c>
@@ -1507,7 +1508,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -1516,10 +1517,10 @@
         <v>285</v>
       </c>
       <c r="P7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="R7" t="s">
         <v>11</v>
@@ -3948,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="K50" t="s">
         <v>1</v>
@@ -3957,16 +3958,19 @@
         <v>2</v>
       </c>
       <c r="M50">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N50">
         <v>2</v>
       </c>
+      <c r="O50">
+        <v>285</v>
+      </c>
       <c r="P50" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R50" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S50" t="s">
         <v>30</v>
@@ -3995,13 +3999,13 @@
         <v>64</v>
       </c>
       <c r="H51">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I51" t="s">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K51" t="s">
         <v>1</v>
@@ -4010,16 +4014,19 @@
         <v>2</v>
       </c>
       <c r="M51">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="N51">
         <v>2</v>
       </c>
+      <c r="O51">
+        <v>285</v>
+      </c>
       <c r="P51" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="R51" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="S51" t="s">
         <v>30</v>
@@ -4048,13 +4055,13 @@
         <v>64</v>
       </c>
       <c r="H52">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I52" t="s">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="K52" t="s">
         <v>1</v>
@@ -4063,16 +4070,19 @@
         <v>2</v>
       </c>
       <c r="M52">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="N52">
         <v>2</v>
       </c>
+      <c r="O52">
+        <v>285</v>
+      </c>
       <c r="P52" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="R52" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S52" t="s">
         <v>30</v>
@@ -4101,13 +4111,13 @@
         <v>64</v>
       </c>
       <c r="H53">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I53" t="s">
         <v>0</v>
       </c>
       <c r="J53">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K53" t="s">
         <v>1</v>
@@ -4116,16 +4126,22 @@
         <v>2</v>
       </c>
       <c r="M53">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="O53">
+        <v>285</v>
       </c>
       <c r="P53" t="s">
-        <v>71</v>
+        <v>88</v>
+      </c>
+      <c r="R53" t="s">
+        <v>89</v>
       </c>
       <c r="S53" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
@@ -4151,34 +4167,37 @@
         <v>64</v>
       </c>
       <c r="H54">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I54" t="s">
         <v>0</v>
       </c>
       <c r="J54">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="K54" t="s">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="L54" t="s">
         <v>2</v>
       </c>
       <c r="M54">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="N54">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="O54">
+        <v>285</v>
       </c>
       <c r="P54" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="R54" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="S54" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
@@ -4210,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="K55" t="s">
         <v>1</v>
@@ -4219,13 +4238,16 @@
         <v>2</v>
       </c>
       <c r="M55">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N55">
         <v>2</v>
       </c>
+      <c r="O55">
+        <v>285</v>
+      </c>
       <c r="P55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="S55" t="s">
         <v>30</v>
@@ -4254,13 +4276,13 @@
         <v>64</v>
       </c>
       <c r="H56">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I56" t="s">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K56" t="s">
         <v>1</v>
@@ -4269,19 +4291,19 @@
         <v>2</v>
       </c>
       <c r="M56">
-        <v>175</v>
-      </c>
-      <c r="N56">
-        <v>2</v>
+        <v>212</v>
+      </c>
+      <c r="O56">
+        <v>285</v>
       </c>
       <c r="P56" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="R56" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="S56" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
@@ -4307,31 +4329,34 @@
         <v>64</v>
       </c>
       <c r="H57">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I57" t="s">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="K57" t="s">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="L57" t="s">
         <v>2</v>
       </c>
       <c r="M57">
-        <v>176</v>
-      </c>
-      <c r="N57">
-        <v>2</v>
+        <v>215</v>
+      </c>
+      <c r="O57">
+        <v>285</v>
       </c>
       <c r="P57" t="s">
-        <v>77</v>
+        <v>104</v>
+      </c>
+      <c r="R57" t="s">
+        <v>94</v>
       </c>
       <c r="S57" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
@@ -4357,13 +4382,13 @@
         <v>64</v>
       </c>
       <c r="H58">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I58" t="s">
         <v>0</v>
       </c>
       <c r="J58">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="K58" t="s">
         <v>1</v>
@@ -4372,19 +4397,19 @@
         <v>2</v>
       </c>
       <c r="M58">
-        <v>177</v>
-      </c>
-      <c r="N58">
-        <v>2</v>
+        <v>242</v>
+      </c>
+      <c r="O58">
+        <v>285</v>
       </c>
       <c r="P58" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="R58" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="S58" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
@@ -4410,13 +4435,13 @@
         <v>64</v>
       </c>
       <c r="H59">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I59" t="s">
         <v>0</v>
       </c>
       <c r="J59">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K59" t="s">
         <v>1</v>
@@ -4425,19 +4450,16 @@
         <v>2</v>
       </c>
       <c r="M59">
-        <v>178</v>
-      </c>
-      <c r="N59">
-        <v>2</v>
+        <v>246</v>
+      </c>
+      <c r="O59">
+        <v>285</v>
       </c>
       <c r="P59" t="s">
-        <v>79</v>
-      </c>
-      <c r="R59" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="S59" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
@@ -4463,13 +4485,13 @@
         <v>64</v>
       </c>
       <c r="H60">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I60" t="s">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="K60" t="s">
         <v>1</v>
@@ -4478,16 +4500,16 @@
         <v>2</v>
       </c>
       <c r="M60">
-        <v>179</v>
-      </c>
-      <c r="N60">
-        <v>2</v>
+        <v>249</v>
+      </c>
+      <c r="O60">
+        <v>285</v>
       </c>
       <c r="P60" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="S60" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
@@ -4513,13 +4535,13 @@
         <v>64</v>
       </c>
       <c r="H61">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I61" t="s">
         <v>0</v>
       </c>
       <c r="J61">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="K61" t="s">
         <v>1</v>
@@ -4528,19 +4550,16 @@
         <v>2</v>
       </c>
       <c r="M61">
-        <v>180</v>
-      </c>
-      <c r="N61">
-        <v>2</v>
+        <v>251</v>
+      </c>
+      <c r="O61">
+        <v>285</v>
       </c>
       <c r="P61" t="s">
-        <v>82</v>
-      </c>
-      <c r="R61" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="S61" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
@@ -4566,13 +4585,13 @@
         <v>64</v>
       </c>
       <c r="H62">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I62" t="s">
         <v>0</v>
       </c>
       <c r="J62">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="K62" t="s">
         <v>1</v>
@@ -4581,16 +4600,16 @@
         <v>2</v>
       </c>
       <c r="M62">
-        <v>205</v>
-      </c>
-      <c r="N62">
-        <v>3</v>
+        <v>280</v>
+      </c>
+      <c r="O62">
+        <v>285</v>
       </c>
       <c r="P62" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="R62" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="S62" t="s">
         <v>86</v>
@@ -4619,34 +4638,31 @@
         <v>64</v>
       </c>
       <c r="H63">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I63" t="s">
         <v>0</v>
       </c>
       <c r="J63">
+        <v>46</v>
+      </c>
+      <c r="K63" t="s">
+        <v>1</v>
+      </c>
+      <c r="L63" t="s">
+        <v>2</v>
+      </c>
+      <c r="M63">
+        <v>283</v>
+      </c>
+      <c r="O63">
+        <v>285</v>
+      </c>
+      <c r="P63" t="s">
         <v>133</v>
       </c>
-      <c r="K63" t="s">
-        <v>1</v>
-      </c>
-      <c r="L63" t="s">
-        <v>2</v>
-      </c>
-      <c r="M63">
-        <v>206</v>
-      </c>
-      <c r="N63">
-        <v>3</v>
-      </c>
-      <c r="P63" t="s">
-        <v>87</v>
-      </c>
-      <c r="R63" t="s">
-        <v>11</v>
-      </c>
       <c r="S63" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
@@ -4672,13 +4688,13 @@
         <v>64</v>
       </c>
       <c r="H64">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I64" t="s">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K64" t="s">
         <v>1</v>
@@ -4687,19 +4703,16 @@
         <v>2</v>
       </c>
       <c r="M64">
-        <v>207</v>
-      </c>
-      <c r="N64">
-        <v>3</v>
+        <v>286</v>
+      </c>
+      <c r="O64">
+        <v>285</v>
       </c>
       <c r="P64" t="s">
-        <v>88</v>
-      </c>
-      <c r="R64" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="S64" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
@@ -4725,34 +4738,31 @@
         <v>64</v>
       </c>
       <c r="H65">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I65" t="s">
         <v>0</v>
       </c>
       <c r="J65">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="K65" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="L65" t="s">
         <v>2</v>
       </c>
       <c r="M65">
-        <v>208</v>
-      </c>
-      <c r="N65">
-        <v>3</v>
+        <v>289</v>
+      </c>
+      <c r="O65">
+        <v>285</v>
       </c>
       <c r="P65" t="s">
-        <v>91</v>
-      </c>
-      <c r="R65" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="S65" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
@@ -4778,34 +4788,37 @@
         <v>64</v>
       </c>
       <c r="H66">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I66" t="s">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="K66" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="L66" t="s">
         <v>2</v>
       </c>
       <c r="M66">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="N66">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="O66">
+        <v>9</v>
       </c>
       <c r="P66" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="R66" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="S66" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
@@ -4831,34 +4844,34 @@
         <v>64</v>
       </c>
       <c r="H67">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I67" t="s">
         <v>0</v>
       </c>
       <c r="J67">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="L67" t="s">
         <v>2</v>
       </c>
       <c r="M67">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="O67">
+        <v>9</v>
       </c>
       <c r="P67" t="s">
-        <v>95</v>
-      </c>
-      <c r="R67" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="S67" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
@@ -4884,13 +4897,13 @@
         <v>64</v>
       </c>
       <c r="H68">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I68" t="s">
         <v>0</v>
       </c>
       <c r="J68">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K68" t="s">
         <v>1</v>
@@ -4899,16 +4912,19 @@
         <v>2</v>
       </c>
       <c r="M68">
-        <v>211</v>
+        <v>176</v>
+      </c>
+      <c r="N68">
+        <v>2</v>
+      </c>
+      <c r="O68">
+        <v>9</v>
       </c>
       <c r="P68" t="s">
-        <v>97</v>
-      </c>
-      <c r="R68" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S68" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
@@ -4934,13 +4950,13 @@
         <v>64</v>
       </c>
       <c r="H69">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I69" t="s">
         <v>0</v>
       </c>
       <c r="J69">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="K69" t="s">
         <v>1</v>
@@ -4949,16 +4965,19 @@
         <v>2</v>
       </c>
       <c r="M69">
-        <v>212</v>
+        <v>179</v>
+      </c>
+      <c r="N69">
+        <v>2</v>
+      </c>
+      <c r="O69">
+        <v>9</v>
       </c>
       <c r="P69" t="s">
-        <v>99</v>
-      </c>
-      <c r="R69" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="S69" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
@@ -4984,28 +5003,34 @@
         <v>64</v>
       </c>
       <c r="H70">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I70" t="s">
         <v>0</v>
       </c>
       <c r="J70">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="K70" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L70" t="s">
         <v>2</v>
       </c>
       <c r="M70">
-        <v>213</v>
+        <v>205</v>
+      </c>
+      <c r="N70">
+        <v>3</v>
+      </c>
+      <c r="O70">
+        <v>9</v>
       </c>
       <c r="P70" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="R70" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="S70" t="s">
         <v>86</v>
@@ -5034,28 +5059,34 @@
         <v>64</v>
       </c>
       <c r="H71">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I71" t="s">
         <v>0</v>
       </c>
       <c r="J71">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="K71" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="L71" t="s">
         <v>2</v>
       </c>
       <c r="M71">
-        <v>214</v>
+        <v>210</v>
+      </c>
+      <c r="N71">
+        <v>3</v>
+      </c>
+      <c r="O71">
+        <v>9</v>
       </c>
       <c r="P71" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="R71" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="S71" t="s">
         <v>86</v>
@@ -5084,28 +5115,31 @@
         <v>64</v>
       </c>
       <c r="H72">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I72" t="s">
         <v>0</v>
       </c>
       <c r="J72">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="K72" t="s">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="L72" t="s">
         <v>2</v>
       </c>
       <c r="M72">
-        <v>215</v>
+        <v>211</v>
+      </c>
+      <c r="O72">
+        <v>9</v>
       </c>
       <c r="P72" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="R72" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="S72" t="s">
         <v>86</v>
@@ -5151,6 +5185,9 @@
       <c r="M73">
         <v>216</v>
       </c>
+      <c r="O73">
+        <v>9</v>
+      </c>
       <c r="P73" t="s">
         <v>106</v>
       </c>
@@ -5198,6 +5235,9 @@
       <c r="M74">
         <v>217</v>
       </c>
+      <c r="O74">
+        <v>9</v>
+      </c>
       <c r="P74" t="s">
         <v>108</v>
       </c>
@@ -5237,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="J75">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="K75" t="s">
         <v>1</v>
@@ -5246,13 +5286,13 @@
         <v>2</v>
       </c>
       <c r="M75">
-        <v>242</v>
+        <v>244</v>
+      </c>
+      <c r="O75">
+        <v>9</v>
       </c>
       <c r="P75" t="s">
-        <v>109</v>
-      </c>
-      <c r="R75" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="S75" t="s">
         <v>86</v>
@@ -5281,13 +5321,13 @@
         <v>64</v>
       </c>
       <c r="H76">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
         <v>0</v>
       </c>
       <c r="J76">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s">
         <v>1</v>
@@ -5296,13 +5336,13 @@
         <v>2</v>
       </c>
       <c r="M76">
-        <v>243</v>
+        <v>245</v>
+      </c>
+      <c r="O76">
+        <v>9</v>
       </c>
       <c r="P76" t="s">
-        <v>111</v>
-      </c>
-      <c r="R76" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="S76" t="s">
         <v>86</v>
@@ -5331,13 +5371,13 @@
         <v>64</v>
       </c>
       <c r="H77">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I77" t="s">
         <v>0</v>
       </c>
       <c r="J77">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s">
         <v>1</v>
@@ -5346,10 +5386,13 @@
         <v>2</v>
       </c>
       <c r="M77">
-        <v>244</v>
+        <v>248</v>
+      </c>
+      <c r="O77">
+        <v>9</v>
       </c>
       <c r="P77" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="S77" t="s">
         <v>86</v>
@@ -5378,13 +5421,13 @@
         <v>64</v>
       </c>
       <c r="H78">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I78" t="s">
         <v>0</v>
       </c>
       <c r="J78">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K78" t="s">
         <v>1</v>
@@ -5393,10 +5436,13 @@
         <v>2</v>
       </c>
       <c r="M78">
-        <v>245</v>
+        <v>253</v>
+      </c>
+      <c r="O78">
+        <v>9</v>
       </c>
       <c r="P78" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="S78" t="s">
         <v>86</v>
@@ -5425,13 +5471,13 @@
         <v>64</v>
       </c>
       <c r="H79">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I79" t="s">
         <v>0</v>
       </c>
       <c r="J79">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="K79" t="s">
         <v>1</v>
@@ -5440,10 +5486,13 @@
         <v>2</v>
       </c>
       <c r="M79">
-        <v>246</v>
+        <v>278</v>
+      </c>
+      <c r="O79">
+        <v>9</v>
       </c>
       <c r="P79" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="S79" t="s">
         <v>86</v>
@@ -5472,13 +5521,13 @@
         <v>64</v>
       </c>
       <c r="H80">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
       </c>
       <c r="J80">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="K80" t="s">
         <v>1</v>
@@ -5487,16 +5536,16 @@
         <v>2</v>
       </c>
       <c r="M80">
-        <v>247</v>
+        <v>282</v>
+      </c>
+      <c r="O80">
+        <v>9</v>
       </c>
       <c r="P80" t="s">
-        <v>115</v>
-      </c>
-      <c r="R80" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="S80" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
@@ -5522,13 +5571,13 @@
         <v>64</v>
       </c>
       <c r="H81">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I81" t="s">
         <v>0</v>
       </c>
       <c r="J81">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K81" t="s">
         <v>1</v>
@@ -5537,13 +5586,16 @@
         <v>2</v>
       </c>
       <c r="M81">
-        <v>248</v>
+        <v>284</v>
+      </c>
+      <c r="O81">
+        <v>9</v>
       </c>
       <c r="P81" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="S81" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
@@ -5569,13 +5621,13 @@
         <v>64</v>
       </c>
       <c r="H82">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I82" t="s">
         <v>0</v>
       </c>
       <c r="J82">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="K82" t="s">
         <v>1</v>
@@ -5584,13 +5636,19 @@
         <v>2</v>
       </c>
       <c r="M82">
-        <v>249</v>
+        <v>288</v>
+      </c>
+      <c r="O82">
+        <v>9</v>
       </c>
       <c r="P82" t="s">
-        <v>118</v>
+        <v>138</v>
+      </c>
+      <c r="R82" t="s">
+        <v>139</v>
       </c>
       <c r="S82" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
@@ -5616,13 +5674,13 @@
         <v>64</v>
       </c>
       <c r="H83">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="I83" t="s">
         <v>0</v>
       </c>
       <c r="J83">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K83" t="s">
         <v>1</v>
@@ -5631,16 +5689,22 @@
         <v>2</v>
       </c>
       <c r="M83">
-        <v>250</v>
+        <v>171</v>
+      </c>
+      <c r="N83">
+        <v>2</v>
+      </c>
+      <c r="O83">
+        <v>293</v>
       </c>
       <c r="P83" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="R83" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="S83" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
@@ -5666,13 +5730,13 @@
         <v>64</v>
       </c>
       <c r="H84">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I84" t="s">
         <v>0</v>
       </c>
       <c r="J84">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="K84" t="s">
         <v>1</v>
@@ -5681,13 +5745,22 @@
         <v>2</v>
       </c>
       <c r="M84">
-        <v>251</v>
+        <v>173</v>
+      </c>
+      <c r="N84">
+        <v>2</v>
+      </c>
+      <c r="O84">
+        <v>293</v>
       </c>
       <c r="P84" t="s">
-        <v>121</v>
+        <v>72</v>
+      </c>
+      <c r="R84" t="s">
+        <v>73</v>
       </c>
       <c r="S84" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
@@ -5713,13 +5786,13 @@
         <v>64</v>
       </c>
       <c r="H85">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
         <v>0</v>
       </c>
       <c r="J85">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K85" t="s">
         <v>1</v>
@@ -5728,16 +5801,22 @@
         <v>2</v>
       </c>
       <c r="M85">
-        <v>252</v>
+        <v>177</v>
+      </c>
+      <c r="N85">
+        <v>2</v>
+      </c>
+      <c r="O85">
+        <v>293</v>
       </c>
       <c r="P85" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="R85" t="s">
         <v>11</v>
       </c>
       <c r="S85" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
@@ -5763,13 +5842,13 @@
         <v>64</v>
       </c>
       <c r="H86">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="I86" t="s">
         <v>0</v>
       </c>
       <c r="J86">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="K86" t="s">
         <v>1</v>
@@ -5778,13 +5857,22 @@
         <v>2</v>
       </c>
       <c r="M86">
-        <v>253</v>
+        <v>180</v>
+      </c>
+      <c r="N86">
+        <v>2</v>
+      </c>
+      <c r="O86">
+        <v>293</v>
       </c>
       <c r="P86" t="s">
-        <v>123</v>
+        <v>82</v>
+      </c>
+      <c r="R86" t="s">
+        <v>83</v>
       </c>
       <c r="S86" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
@@ -5810,13 +5898,13 @@
         <v>64</v>
       </c>
       <c r="H87">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I87" t="s">
         <v>0</v>
       </c>
       <c r="J87">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="K87" t="s">
         <v>1</v>
@@ -5825,10 +5913,19 @@
         <v>2</v>
       </c>
       <c r="M87">
-        <v>278</v>
+        <v>206</v>
+      </c>
+      <c r="N87">
+        <v>3</v>
+      </c>
+      <c r="O87">
+        <v>293</v>
       </c>
       <c r="P87" t="s">
-        <v>124</v>
+        <v>87</v>
+      </c>
+      <c r="R87" t="s">
+        <v>11</v>
       </c>
       <c r="S87" t="s">
         <v>86</v>
@@ -5857,28 +5954,34 @@
         <v>64</v>
       </c>
       <c r="H88">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I88" t="s">
         <v>0</v>
       </c>
       <c r="J88">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="K88" t="s">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="L88" t="s">
         <v>2</v>
       </c>
       <c r="M88">
-        <v>279</v>
+        <v>209</v>
+      </c>
+      <c r="N88">
+        <v>3</v>
+      </c>
+      <c r="O88">
+        <v>293</v>
       </c>
       <c r="P88" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="R88" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="S88" t="s">
         <v>86</v>
@@ -5907,28 +6010,31 @@
         <v>64</v>
       </c>
       <c r="H89">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I89" t="s">
         <v>0</v>
       </c>
       <c r="J89">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="K89" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L89" t="s">
         <v>2</v>
       </c>
       <c r="M89">
-        <v>280</v>
+        <v>213</v>
+      </c>
+      <c r="O89">
+        <v>293</v>
       </c>
       <c r="P89" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="R89" t="s">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="S89" t="s">
         <v>86</v>
@@ -5957,28 +6063,31 @@
         <v>64</v>
       </c>
       <c r="H90">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I90" t="s">
         <v>0</v>
       </c>
       <c r="J90">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="K90" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L90" t="s">
         <v>2</v>
       </c>
       <c r="M90">
-        <v>281</v>
+        <v>214</v>
+      </c>
+      <c r="O90">
+        <v>293</v>
       </c>
       <c r="P90" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="R90" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="S90" t="s">
         <v>86</v>
@@ -6007,13 +6116,13 @@
         <v>64</v>
       </c>
       <c r="H91">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I91" t="s">
         <v>0</v>
       </c>
       <c r="J91">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="K91" t="s">
         <v>1</v>
@@ -6022,13 +6131,19 @@
         <v>2</v>
       </c>
       <c r="M91">
-        <v>282</v>
+        <v>243</v>
+      </c>
+      <c r="O91">
+        <v>293</v>
       </c>
       <c r="P91" t="s">
-        <v>131</v>
+        <v>111</v>
+      </c>
+      <c r="R91" t="s">
+        <v>11</v>
       </c>
       <c r="S91" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
@@ -6054,13 +6169,13 @@
         <v>64</v>
       </c>
       <c r="H92">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
       </c>
       <c r="J92">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="K92" t="s">
         <v>1</v>
@@ -6069,13 +6184,19 @@
         <v>2</v>
       </c>
       <c r="M92">
-        <v>283</v>
+        <v>247</v>
+      </c>
+      <c r="O92">
+        <v>293</v>
       </c>
       <c r="P92" t="s">
-        <v>133</v>
+        <v>115</v>
+      </c>
+      <c r="R92" t="s">
+        <v>116</v>
       </c>
       <c r="S92" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
@@ -6101,13 +6222,13 @@
         <v>64</v>
       </c>
       <c r="H93">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I93" t="s">
         <v>0</v>
       </c>
       <c r="J93">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="K93" t="s">
         <v>1</v>
@@ -6116,13 +6237,19 @@
         <v>2</v>
       </c>
       <c r="M93">
-        <v>284</v>
+        <v>250</v>
+      </c>
+      <c r="O93">
+        <v>293</v>
       </c>
       <c r="P93" t="s">
-        <v>134</v>
+        <v>119</v>
+      </c>
+      <c r="R93" t="s">
+        <v>120</v>
       </c>
       <c r="S93" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
@@ -6148,13 +6275,13 @@
         <v>64</v>
       </c>
       <c r="H94">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I94" t="s">
         <v>0</v>
       </c>
       <c r="J94">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K94" t="s">
         <v>1</v>
@@ -6163,16 +6290,19 @@
         <v>2</v>
       </c>
       <c r="M94">
-        <v>285</v>
+        <v>252</v>
+      </c>
+      <c r="O94">
+        <v>293</v>
       </c>
       <c r="P94" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="R94" t="s">
         <v>11</v>
       </c>
       <c r="S94" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
@@ -6198,13 +6328,13 @@
         <v>64</v>
       </c>
       <c r="H95">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
       </c>
       <c r="J95">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="K95" t="s">
         <v>1</v>
@@ -6213,13 +6343,19 @@
         <v>2</v>
       </c>
       <c r="M95">
-        <v>286</v>
+        <v>279</v>
+      </c>
+      <c r="O95">
+        <v>293</v>
       </c>
       <c r="P95" t="s">
-        <v>136</v>
+        <v>125</v>
+      </c>
+      <c r="R95" t="s">
+        <v>126</v>
       </c>
       <c r="S95" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
@@ -6245,13 +6381,13 @@
         <v>64</v>
       </c>
       <c r="H96">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I96" t="s">
         <v>0</v>
       </c>
       <c r="J96">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K96" t="s">
         <v>1</v>
@@ -6260,16 +6396,19 @@
         <v>2</v>
       </c>
       <c r="M96">
-        <v>287</v>
+        <v>281</v>
+      </c>
+      <c r="O96">
+        <v>293</v>
       </c>
       <c r="P96" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="R96" t="s">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="S96" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
@@ -6295,13 +6434,13 @@
         <v>64</v>
       </c>
       <c r="H97">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I97" t="s">
         <v>0</v>
       </c>
       <c r="J97">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="K97" t="s">
         <v>1</v>
@@ -6310,13 +6449,16 @@
         <v>2</v>
       </c>
       <c r="M97">
-        <v>288</v>
+        <v>285</v>
+      </c>
+      <c r="O97">
+        <v>293</v>
       </c>
       <c r="P97" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="R97" t="s">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="S97" t="s">
         <v>132</v>
@@ -6351,7 +6493,7 @@
         <v>0</v>
       </c>
       <c r="J98">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="K98" t="s">
         <v>1</v>
@@ -6360,10 +6502,16 @@
         <v>2</v>
       </c>
       <c r="M98">
-        <v>289</v>
+        <v>287</v>
+      </c>
+      <c r="O98">
+        <v>293</v>
       </c>
       <c r="P98" t="s">
-        <v>140</v>
+        <v>137</v>
+      </c>
+      <c r="R98" t="s">
+        <v>11</v>
       </c>
       <c r="S98" t="s">
         <v>132</v>
@@ -6392,28 +6540,25 @@
         <v>64</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I99" t="s">
         <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>141</v>
+        <v>194</v>
       </c>
       <c r="K99" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L99" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M99">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="P99" t="s">
-        <v>142</v>
-      </c>
-      <c r="R99" t="s">
-        <v>143</v>
+        <v>195</v>
       </c>
       <c r="S99" t="s">
         <v>132</v>
@@ -6442,25 +6587,25 @@
         <v>64</v>
       </c>
       <c r="H100">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I100" t="s">
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="K100" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L100" t="s">
         <v>2</v>
       </c>
       <c r="M100">
-        <v>291</v>
+        <v>335</v>
       </c>
       <c r="P100" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="S100" t="s">
         <v>132</v>
@@ -6489,25 +6634,25 @@
         <v>64</v>
       </c>
       <c r="H101">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I101" t="s">
         <v>0</v>
       </c>
       <c r="J101" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="K101" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L101" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M101">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="P101" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="S101" t="s">
         <v>132</v>
@@ -6536,25 +6681,28 @@
         <v>64</v>
       </c>
       <c r="H102">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I102" t="s">
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="K102" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L102" t="s">
         <v>2</v>
       </c>
       <c r="M102">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="P102" t="s">
-        <v>149</v>
+        <v>172</v>
+      </c>
+      <c r="R102" t="s">
+        <v>173</v>
       </c>
       <c r="S102" t="s">
         <v>132</v>
@@ -6583,25 +6731,25 @@
         <v>64</v>
       </c>
       <c r="H103">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I103" t="s">
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K103" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L103" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M103">
-        <v>295</v>
+        <v>337</v>
       </c>
       <c r="P103" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="S103" t="s">
         <v>132</v>
@@ -6630,25 +6778,25 @@
         <v>64</v>
       </c>
       <c r="H104">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I104" t="s">
         <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="K104" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L104" t="s">
         <v>2</v>
       </c>
       <c r="M104">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="P104" t="s">
-        <v>153</v>
+        <v>202</v>
       </c>
       <c r="S104" t="s">
         <v>132</v>
@@ -6677,25 +6825,28 @@
         <v>64</v>
       </c>
       <c r="H105">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I105" t="s">
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="K105" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L105" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M105">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="P105" t="s">
-        <v>155</v>
+        <v>179</v>
+      </c>
+      <c r="R105" t="s">
+        <v>180</v>
       </c>
       <c r="S105" t="s">
         <v>132</v>
@@ -6724,25 +6875,25 @@
         <v>64</v>
       </c>
       <c r="H106">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I106" t="s">
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="K106" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L106" t="s">
         <v>2</v>
       </c>
       <c r="M106">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="P106" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="S106" t="s">
         <v>132</v>
@@ -6771,25 +6922,28 @@
         <v>64</v>
       </c>
       <c r="H107">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I107" t="s">
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="K107" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L107" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M107">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="P107" t="s">
-        <v>159</v>
+        <v>198</v>
+      </c>
+      <c r="R107" t="s">
+        <v>199</v>
       </c>
       <c r="S107" t="s">
         <v>132</v>
@@ -6818,25 +6972,28 @@
         <v>64</v>
       </c>
       <c r="H108">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I108" t="s">
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="K108" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L108" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M108">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="P108" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="R108" t="s">
+        <v>176</v>
       </c>
       <c r="S108" t="s">
         <v>132</v>
@@ -6865,28 +7022,25 @@
         <v>64</v>
       </c>
       <c r="H109">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I109" t="s">
         <v>0</v>
       </c>
       <c r="J109" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="K109" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L109" t="s">
         <v>2</v>
       </c>
       <c r="M109">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="P109" t="s">
-        <v>163</v>
-      </c>
-      <c r="R109" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="S109" t="s">
         <v>132</v>
@@ -6915,25 +7069,25 @@
         <v>64</v>
       </c>
       <c r="H110">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I110" t="s">
         <v>0</v>
       </c>
       <c r="J110" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="K110" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L110" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M110">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="P110" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="S110" t="s">
         <v>132</v>
@@ -6962,25 +7116,25 @@
         <v>64</v>
       </c>
       <c r="H111">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I111" t="s">
         <v>0</v>
       </c>
       <c r="J111" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="K111" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="L111" t="s">
         <v>2</v>
       </c>
       <c r="M111">
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="P111" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="S111" t="s">
         <v>132</v>
@@ -7009,13 +7163,13 @@
         <v>64</v>
       </c>
       <c r="H112">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I112" t="s">
         <v>0</v>
       </c>
       <c r="J112" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="K112" t="s">
         <v>170</v>
@@ -7024,10 +7178,10 @@
         <v>105</v>
       </c>
       <c r="M112">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="P112" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="S112" t="s">
         <v>132</v>
@@ -7056,13 +7210,13 @@
         <v>64</v>
       </c>
       <c r="H113">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I113" t="s">
         <v>0</v>
       </c>
       <c r="J113" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="K113" t="s">
         <v>170</v>
@@ -7071,13 +7225,10 @@
         <v>2</v>
       </c>
       <c r="M113">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="P113" t="s">
-        <v>172</v>
-      </c>
-      <c r="R113" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="S113" t="s">
         <v>132</v>
@@ -7106,13 +7257,13 @@
         <v>64</v>
       </c>
       <c r="H114">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="I114" t="s">
         <v>0</v>
       </c>
       <c r="J114" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="K114" t="s">
         <v>170</v>
@@ -7121,13 +7272,10 @@
         <v>105</v>
       </c>
       <c r="M114">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="P114" t="s">
-        <v>175</v>
-      </c>
-      <c r="R114" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="S114" t="s">
         <v>132</v>
@@ -7156,13 +7304,13 @@
         <v>64</v>
       </c>
       <c r="H115">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="I115" t="s">
         <v>0</v>
       </c>
       <c r="J115" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="K115" t="s">
         <v>170</v>
@@ -7171,10 +7319,10 @@
         <v>2</v>
       </c>
       <c r="M115">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="P115" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="S115" t="s">
         <v>132</v>
@@ -7203,13 +7351,13 @@
         <v>64</v>
       </c>
       <c r="H116">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="I116" t="s">
         <v>0</v>
       </c>
       <c r="J116" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="K116" t="s">
         <v>170</v>
@@ -7218,13 +7366,10 @@
         <v>105</v>
       </c>
       <c r="M116">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="P116" t="s">
-        <v>179</v>
-      </c>
-      <c r="R116" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="S116" t="s">
         <v>132</v>
@@ -7253,13 +7398,13 @@
         <v>64</v>
       </c>
       <c r="H117">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="I117" t="s">
         <v>0</v>
       </c>
       <c r="J117" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="K117" t="s">
         <v>170</v>
@@ -7268,10 +7413,10 @@
         <v>2</v>
       </c>
       <c r="M117">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="P117" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="S117" t="s">
         <v>132</v>
@@ -7300,25 +7445,25 @@
         <v>64</v>
       </c>
       <c r="H118">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I118" t="s">
         <v>0</v>
       </c>
       <c r="J118" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="K118" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M118">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="P118" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="S118" t="s">
         <v>132</v>
@@ -7347,25 +7492,28 @@
         <v>64</v>
       </c>
       <c r="H119">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I119" t="s">
         <v>0</v>
       </c>
       <c r="J119" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="K119" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L119" t="s">
         <v>2</v>
       </c>
       <c r="M119">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="P119" t="s">
-        <v>184</v>
+        <v>163</v>
+      </c>
+      <c r="R119" t="s">
+        <v>164</v>
       </c>
       <c r="S119" t="s">
         <v>132</v>
@@ -7394,25 +7542,25 @@
         <v>64</v>
       </c>
       <c r="H120">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I120" t="s">
         <v>0</v>
       </c>
       <c r="J120" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="K120" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L120" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M120">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="P120" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="S120" t="s">
         <v>132</v>
@@ -7441,25 +7589,25 @@
         <v>64</v>
       </c>
       <c r="H121">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I121" t="s">
         <v>0</v>
       </c>
       <c r="J121" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="K121" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L121" t="s">
         <v>2</v>
       </c>
       <c r="M121">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="P121" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="S121" t="s">
         <v>132</v>
@@ -7488,25 +7636,25 @@
         <v>64</v>
       </c>
       <c r="H122">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I122" t="s">
         <v>0</v>
       </c>
       <c r="J122" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="K122" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L122" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M122">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="P122" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="S122" t="s">
         <v>132</v>
@@ -7535,25 +7683,25 @@
         <v>64</v>
       </c>
       <c r="H123">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I123" t="s">
         <v>0</v>
       </c>
       <c r="J123" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="K123" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L123" t="s">
         <v>2</v>
       </c>
       <c r="M123">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="P123" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="S123" t="s">
         <v>132</v>
@@ -7582,25 +7730,25 @@
         <v>64</v>
       </c>
       <c r="H124">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I124" t="s">
         <v>0</v>
       </c>
       <c r="J124" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="K124" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L124" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M124">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="P124" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="S124" t="s">
         <v>132</v>
@@ -7629,25 +7777,25 @@
         <v>64</v>
       </c>
       <c r="H125">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I125" t="s">
         <v>0</v>
       </c>
       <c r="J125" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="K125" t="s">
         <v>170</v>
       </c>
       <c r="L125" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M125">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="P125" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="S125" t="s">
         <v>132</v>
@@ -7676,25 +7824,25 @@
         <v>64</v>
       </c>
       <c r="H126">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="I126" t="s">
         <v>0</v>
       </c>
       <c r="J126" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="K126" t="s">
         <v>170</v>
       </c>
       <c r="L126" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M126">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="P126" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="S126" t="s">
         <v>132</v>
@@ -7723,25 +7871,25 @@
         <v>64</v>
       </c>
       <c r="H127">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I127" t="s">
         <v>0</v>
       </c>
       <c r="J127" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K127" t="s">
         <v>170</v>
       </c>
       <c r="L127" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="M127">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="P127" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="S127" t="s">
         <v>132</v>
@@ -7770,28 +7918,25 @@
         <v>64</v>
       </c>
       <c r="H128">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I128" t="s">
         <v>0</v>
       </c>
       <c r="J128" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="K128" t="s">
         <v>170</v>
       </c>
       <c r="L128" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M128">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="P128" t="s">
-        <v>198</v>
-      </c>
-      <c r="R128" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="S128" t="s">
         <v>132</v>
@@ -7820,13 +7965,13 @@
         <v>64</v>
       </c>
       <c r="H129">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I129" t="s">
         <v>0</v>
       </c>
       <c r="J129" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K129" t="s">
         <v>170</v>
@@ -7835,10 +7980,10 @@
         <v>105</v>
       </c>
       <c r="M129">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="P129" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="S129" t="s">
         <v>132</v>
@@ -7867,13 +8012,13 @@
         <v>64</v>
       </c>
       <c r="H130">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I130" t="s">
         <v>0</v>
       </c>
       <c r="J130" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K130" t="s">
         <v>170</v>
@@ -7882,10 +8027,10 @@
         <v>2</v>
       </c>
       <c r="M130">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="P130" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="S130" t="s">
         <v>132</v>
@@ -7914,13 +8059,13 @@
         <v>64</v>
       </c>
       <c r="H131">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I131" t="s">
         <v>0</v>
       </c>
       <c r="J131" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="K131" t="s">
         <v>170</v>
@@ -7929,10 +8074,10 @@
         <v>105</v>
       </c>
       <c r="M131">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="P131" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="S131" t="s">
         <v>132</v>
@@ -7961,13 +8106,13 @@
         <v>64</v>
       </c>
       <c r="H132">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I132" t="s">
         <v>0</v>
       </c>
       <c r="J132" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="K132" t="s">
         <v>170</v>
@@ -7976,10 +8121,10 @@
         <v>2</v>
       </c>
       <c r="M132">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="P132" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="S132" t="s">
         <v>132</v>
@@ -8008,25 +8153,25 @@
         <v>64</v>
       </c>
       <c r="H133">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I133" t="s">
         <v>0</v>
       </c>
       <c r="J133" t="s">
-        <v>206</v>
+        <v>154</v>
       </c>
       <c r="K133" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L133" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M133">
-        <v>343</v>
+        <v>297</v>
       </c>
       <c r="P133" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="S133" t="s">
         <v>132</v>
@@ -8055,25 +8200,28 @@
         <v>64</v>
       </c>
       <c r="H134">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I134" t="s">
         <v>0</v>
       </c>
       <c r="J134" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="K134" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L134" t="s">
         <v>2</v>
       </c>
       <c r="M134">
-        <v>344</v>
+        <v>290</v>
       </c>
       <c r="P134" t="s">
-        <v>208</v>
+        <v>142</v>
+      </c>
+      <c r="R134" t="s">
+        <v>143</v>
       </c>
       <c r="S134" t="s">
         <v>132</v>
@@ -8102,25 +8250,25 @@
         <v>64</v>
       </c>
       <c r="H135">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="I135" t="s">
         <v>0</v>
       </c>
       <c r="J135" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="K135" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L135" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M135">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="P135" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="S135" t="s">
         <v>132</v>
@@ -8149,25 +8297,25 @@
         <v>64</v>
       </c>
       <c r="H136">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I136" t="s">
         <v>0</v>
       </c>
       <c r="J136" t="s">
-        <v>209</v>
+        <v>144</v>
       </c>
       <c r="K136" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L136" t="s">
         <v>2</v>
       </c>
       <c r="M136">
-        <v>346</v>
+        <v>291</v>
       </c>
       <c r="P136" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="S136" t="s">
         <v>132</v>
@@ -8196,25 +8344,25 @@
         <v>64</v>
       </c>
       <c r="H137">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I137" t="s">
         <v>0</v>
       </c>
       <c r="J137" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="K137" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L137" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="M137">
-        <v>347</v>
+        <v>299</v>
       </c>
       <c r="P137" t="s">
-        <v>213</v>
+        <v>159</v>
       </c>
       <c r="S137" t="s">
         <v>132</v>
@@ -8243,31 +8391,34 @@
         <v>64</v>
       </c>
       <c r="H138">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I138" t="s">
         <v>0</v>
       </c>
       <c r="J138" t="s">
-        <v>212</v>
+        <v>146</v>
       </c>
       <c r="K138" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="L138" t="s">
         <v>2</v>
       </c>
       <c r="M138">
-        <v>348</v>
+        <v>292</v>
       </c>
       <c r="P138" t="s">
-        <v>214</v>
+        <v>147</v>
       </c>
       <c r="S138" t="s">
         <v>132</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S139">
+    <sortCondition ref="F1:F139"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>